--- a/output/campaign_Vive_Living.xlsx
+++ b/output/campaign_Vive_Living.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,4821 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>573128530946</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Henderson J</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>60254756022</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>573122132304</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>60536057444</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>573113154911</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jesus Arbey</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>60140573201</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>573223364203</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>60078390166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>573045247486</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>60052711227</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>573183644257</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Angel Alfonso</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60081594028</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>573013103545</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rubiela</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60141627307</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>573015986977</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>59248180750</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>573144435695</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Oswaldo</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>60152442508</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>573001234567</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>59495430148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>573136151713</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Flavio</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>60041794183</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>573146177060</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>59701500254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>573123971509</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>59785432117</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>573045854060</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Julian Esteban</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>59954011144</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>573174029325</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Natalia Maria</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>60292031366</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>573213833904</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Erika J</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>60256103180</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>573188153484</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Willyam Leonardo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>59327045746</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>573006469858</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>60120113152</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>573171609587</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>60671475634</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>573008364862</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>59792432549</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>573128918774</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yesid</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>60051379811</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>573173771222</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>60053477228</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>573013714710</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>59562397352</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>573234957304</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yuliana Maria</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>60204869197</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>573148825616</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yeye</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>59937234601</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>573001024011</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jhonatan</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>60036554279</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>573104504943</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>60334270076</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>573137936576</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Johnathan</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>60052551444</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>573183505414</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Luis Miguel</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>59806724174</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>573155049342</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>60076455338</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>573006537888</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>59545538874</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>573116002971</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oswaldo</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>59806320800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>573246660029</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>60199552919</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>573126438647</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>59230370955</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>573124685782</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yuly</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>60676345265</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>573188372111</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gerson Iván</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>60236770726</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>573017727937</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wilmar</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>59489816335</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>573223784677</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wilver Arley</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>59319398799</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>573026139975</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>60233445305</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>573209071682</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>59483275180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>573127707349</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Paula Andrea Usuga</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>59235729249</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>573206888624</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>60650851625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>573206956555</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gonzalo</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>60076778402</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>573137802259</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>60052848720</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>573137317794</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>60075819854</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>573104755972</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>60206837554</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>573187903268</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Luis Alfonso</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>60119199778</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>573017919626</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>60204104314</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>573022574096</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jaime Rafael Guerrero</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>60049553772</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>573015254631</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>60075823669</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>573117250924</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>59431345024</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>573143941415</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jose German</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>60155580236</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>573116130678</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>60205750594</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>573023851422</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>60275067026</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>573117410376</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Alejo</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>60050158487</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>573006859228</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Melani Gisella</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>59155908376</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>573148300224</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>60050925469</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>573108374163</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>60041918069</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>573118445692</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Luis Alberto</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>60072678250</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>573148183788</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>60074965037</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>573244812072</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jesus Gallardo</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>60184866825</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>573006526152</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>59649836072</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>573137447977</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Arles</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>60295390587</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>573128325777</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Duvian</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>60075426090</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>573112270807</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>60152290420</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>573113798244</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sebastian Escobar</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>59806664118</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>573124147943</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mj-tech</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>60459916544</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>573133611464</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>60164388651</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>573014362120</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Saul Antonio</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>60563416109</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>573103724743</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>60052292458</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>573016623669</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Simón Álvarez</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>60222398034</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>573003033435</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>59332814420</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>573122655340</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lina María</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>59375212920</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>573017843743</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>60249577827</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>573103896426</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>60110034872</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>573504401811</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>59702228803</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>573006516157</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>60241343093</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>573163325432</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Paola Andrea</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>59991892125</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>573132686243</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>60128953247</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>573508142748</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Edwin G.</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>59478550334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>573103989148</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>60165463064</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>573143930714</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jorge L</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>59665356600</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>573013991671</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Eduar</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>60658507123</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>573505801880</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Víctor Manuel</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>59483891256</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>573017566143</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>59472272398</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>573007805847</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>60156958302</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>573117617952</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Carloa</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>60239413318</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>573202357808</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gloria Isabel</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>59576988968</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>573144583611</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>60330723693</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>573148976675</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Alvaro</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>60315214345</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>573104249325</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Luis German</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>60034343528</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>573017527438</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>59232842926</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>573012852701</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Luis Felipe</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>59245417747</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>573113208654</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>60511671945</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>573161885979</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>60589555261</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>573117628969</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>60074667278</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>573173722491</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wilmar</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>60334762297</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>573024017303</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>60668203659</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>573007368015</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Fabian Esteban</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>59235204244</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>573183244600</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>John Fredy</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>60056034905</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>573146184110</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>59686797167</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>573233051107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>59850832706</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>573174245213</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Luis Gonzaga</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>60257242204</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>573145221590</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Agustín</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>60232212508</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>573164702242</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Bayron</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>60136677395</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>573013176944</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>59764731700</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>573207003332</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>60189204010</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>573104265819</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Álvaro</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>60259895215</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>573204116132</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>60312034370</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>573144179796</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>59237618024</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>573174144706</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Elver</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>60325277099</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>573166923170</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>59474165062</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>573057514682</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>59490437678</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>573167036258</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Marcial</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>60299440433</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>573207248168</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Luz Mila</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>60077165427</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>573107176499</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Víctor Manuel</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>60180561235</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>573043761062</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ana Dely</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>60259969432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>573184472310</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>José Fernando</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>60643427445</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>573013382948</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>60299977061</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>573014390808</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>60540220463</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>573225235334</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hernando</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>60314609228</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>573006977846</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>60591741331</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>573008375110</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>60292651541</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>573187169190</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ismael</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>60050827943</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>573156658887</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Carlos Manuel</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>60202537050</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>573506135023</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jose Alejandro</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>60041219106</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>573006086033</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Victor Eduardo</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>59318655264</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>573504210957</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hector Andres</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>59853181218</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>573014319008</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Alejo</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>60305729324</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>573116753594</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Walter</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>59437802061</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>573147916271</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Maria Paula</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>60054003021</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>573157794665</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Maria V</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>60600958094</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>573206811952</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Carlos Andrés Palacios Agudelo</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>60105955844</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>573004459271</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>59328663993</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>573137885296</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>60651427155</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>573133096818</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>60334578761</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>573004943764</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Katherinne</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>59462319189</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>573052764205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Julio Cesar</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>60560808319</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>573226674165</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Manuel José</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>60666927909</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>573014715339</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>60314887335</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>573108467896</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>60058002465</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>573146815005</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>60239620749</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>573133778218</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>59686268807</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>573016741340</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Franco Andres</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>59575644023</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>573002208793</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>59389873247</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>573009590991</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Luzedi</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>60237826981</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>573003489154</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Juan Felipe</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>59548967568</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>573189225888</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Filadelfo</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>60540227445</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>573124500902</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Juan Pablo</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>60709179932</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>573052200111</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>60239143534</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>573148813835</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Cerli Mildrey</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>60254710620</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>573163682075</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ivon</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>59386982665</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>573008163481</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>60073985286</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>573163540405</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>59124234093</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>573218339208</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Federico</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>59463287737</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>573147730003</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>60077530900</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>573143440006</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Antonio José</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>59702666893</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>573103951864</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>60349215770</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>573212070244</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Javier Mauricio</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>60051703362</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>573043652040</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>60269121883</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>573217511620</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>59806677899</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>573168326002</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>59805321906</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>573228195106</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jorge Armando</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>59530935216</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>573108329228</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>John Jairo</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>60176873850</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>573136569673</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>60141710372</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>573183001456</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Luis Vasquez Hipnoterapeuta Y Coach En</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>59666417047</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>573024709790</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tomás Moncada</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>59419990935</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>573043460864</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>60533453708</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>573147303372</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>59467409049</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>573187436101</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Raymond</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>60561781626</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>573117194474</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>60271874078</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>573103258382</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>59131347460</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>573012751512</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>60200643725</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>573164421499</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>60052530800</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>573001119374</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>60237899961</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>573046689664</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>59498831757</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>573122278261</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>59806409362</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>573016091192</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Jonathan Andres</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>59497202815</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>573102027190</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>60593145921</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>573108287526</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>60174763058</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>573006134560</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Jorge René</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>60052791562</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>573013452168</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Elena Beatriz</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>60689664914</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>573005766167</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>59941198142</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>573002394302</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>59445649017</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>573007041014</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>60238763899</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>573174275983</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>60689392984</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>573155100153</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>60217997934</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>573124577943</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>59806329102</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>573108253701</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Gladimir</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>60334572168</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>573008057436</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Jose Jaime</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>60050949464</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>573156363636</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>60074269823</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>573006108484</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Luis Alejandro</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>59031904880</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>573011208076</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Delio</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>60387906896</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>573103613806</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>60165683361</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>573128721411</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>59470911295</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>573507270670</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Juan Angel</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>59459402851</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>573163447986</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>60613369720</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>573185233450</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ana Beatriz</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>60164641447</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>573209188950</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sandra Patricia</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>60155714737</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>573155683910</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Beatriz Helena</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>59697038946</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>573116351670</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Leon Augusto</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>59331274014</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>573117643335</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Carlos Alberto</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>60270592295</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>573016689903</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Marta Cecilia</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>60260012890</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>573002492198</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>59574513284</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>573003067061</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>59523350934</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>573122773145</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Johanna Marcela</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>60445218411</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>573167886774</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>José Nelson</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>60327641876</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>573016592548</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Jorge Eduardo</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>60196455786</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>573128347587</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Iván Darío</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>59695115423</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>573013377320</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Adriana Patricia</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>60204414255</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>573116094724</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>59681481620</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>573222516049</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Cesar Fernando</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>60050448171</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>573003081235</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>59757415683</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>573017074390</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>60673776423</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>573128033653</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Aima Valentina</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>60604378181</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>573046568885</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>60466678062</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>573016154557</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Dr. Oscar</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>60218918163</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>573104597427</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>60530577336</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>573163430459</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>60173093739</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>573007866912</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Fabian Andres</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>59838408290</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>573122886556</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>60167225418</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>573007246984</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>60665693786</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>573183350774</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>59312686736</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>573192341100</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>60201387573</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>573176408056</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>60531476845</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>573180278436</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>60713209695</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>573124754275</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Felipe Garzón</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>60014165825</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>573008784196</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>59479630689</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>573013571001</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Eduardo Arias Cadavid</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>59216705843</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>573126496480</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>60334006187</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>573137626474</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Karina</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>59806484576</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>573124860471</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Esteban Bautista</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>59679101225</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>573222150910</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>60051421298</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>573218605452</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>60146426227</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>573045380402</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Cristian Camilo</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>59538457660</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>573207101870</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>60420884514</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>573204543149</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>59841187908</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>573014716531</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Dra. Viviana Cortes</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>60315621674</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>573147712566</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Alejandra Marcela</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>60074512813</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>573137826254</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Dora</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>60077025360</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>573103876683</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>59122588777</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>573175195405</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Fundacion</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>60238908573</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>573206054434</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Yazmin</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>60696265378</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>573008165001</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Liliana</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>60055063924</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>573016425381</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Enith Teresa</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>60656933724</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>573103946588</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>59806415887</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>573212161668</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>60073946917</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>573104272021</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mara Camila</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>59769959290</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>573104625410</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Blanca</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>60074181485</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>573136588384</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>60631112118</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>573122860109</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>59481178461</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>573164601889</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>59793467486</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>573217519687</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>59559782984</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>573104360382</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Ruben</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>59759610218</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>573118539115</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>60075342520</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>573186496232</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Pili</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>59700476680</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>573188363997</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>60403359092</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>573016756082</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Eliana</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>59552681479</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>573007818092</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>59806694766</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>573008822373</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Daniel Jose</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>60401334136</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>573102465436</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Yamile Chica</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>59659046186</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>573013968367</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Natalia Gallego</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>59806642054</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>573146309255</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Maria Paulina</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>60219150914</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>573117624362</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>60164942406</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>573116306422</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lina Maria</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>60240124555</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>573148290668</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Katherine Trespalacios</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>59752419965</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>573136607972</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Jacobo</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>60239726961</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>573135899407</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Joaquin</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>60466901112</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>573177831322</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>59337280940</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>573007971530</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>60074206348</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>573167409085</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Nury Johana</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>57979973155</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>573137484026</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>59272935535</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>573104061112</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Alexandra Grisales Vahos</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>60253550420</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>573113926575</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Remberto Luis</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>60063314025</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>573202360088</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>59476487582</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>573218171735</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>60294354789</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>573214383059</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Maria Alexandra</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>60180122112</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>573104382627</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>59806536881</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>573053696055</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>60143326059</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>573161347211</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Sergio Andrés</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>60050675467</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>573128166669</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>60187947172</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>573017957102</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Juanes</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>60532011823</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>573044613245</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>60153435969</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>573153262401</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Natalia Andrea</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>59728016457</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>573128952007</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>David Llano</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>59432784725</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>573128869333</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>60023008891</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>573023657210</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>59806677898</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>573193526430</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Andres Felipe</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>60041216799</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>573007782877</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Jesus David</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>60056360788</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>573203425658</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>60239414273</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>573114079721</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>60115300789</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>573017853959</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>60139953301</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>573044383282</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>59805097528</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>573173093693</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Yaky</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>60607024481</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>573126752038</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Isaias</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>60219075355</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>573122705926</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Laura Giraldo</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>59267526955</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>573004328277</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>60074626698</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>573007639972</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Angie Tatiana</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>60097461867</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>573206043216</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>60160456212</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>573012404261</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>59421061539</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>573133863170</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>59720649354</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>573222168902</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lina</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>60106875224</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>573104435563</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>60076679786</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>573105481020</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Luis Orlando</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>60077085452</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>573104477331</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ana Maria</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>60551017732</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>573132550308</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>60013864628</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>573137370103</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>60304489739</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>573122063372</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Shirley Johana</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>59548508849</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>573108483363</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Ana Maria</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>60379234216</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>573122178530</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>60632046370</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>573148889243</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>60079679059</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>573146152218</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>60453620547</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>573144580632</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Laura Mercadeo</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>60059102390</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>573135748341</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>59570932624</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>573043460864</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>60539594514</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>573124457430</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>59570787255</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>573127938080</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>60074896916</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>573187620912</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>60676243800</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>573205309193</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Álvaro Fernando</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>60139210154</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>573006545177</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>59332807266</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>573116204753</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Juanjose Galvis</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>59247487496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/campaign_Vive_Living.xlsx
+++ b/output/campaign_Vive_Living.xlsx
@@ -441,11 +441,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Henderson J</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>60254756022</v>
+          <t>Henderson J Berrios Olivera</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>60254756022</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -456,11 +458,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>60536057444</v>
+          <t>Mario Arango Ossa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>60536057444</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -471,11 +475,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jesus Arbey</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>60140573201</v>
+          <t>Jesus Arbey Gaviria Hernandez</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>60140573201</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -486,11 +492,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>60078390166</v>
+          <t>Santiago Garzón</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>60078390166</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -501,11 +509,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>60052711227</v>
+          <t>Carlos Otero</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>60052711227</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -516,11 +526,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Angel Alfonso</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>60081594028</v>
+          <t>Angel Alfonso Ramirez Díaz</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>60081594028</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -531,11 +543,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rubiela</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>60141627307</v>
+          <t>Rubiela Molina</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>60141627307</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -546,11 +560,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aida</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>59248180750</v>
+          <t>Aida Medina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>59248180750</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -561,11 +577,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>60152442508</v>
+          <t>Oswaldo Ome</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>60152442508</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -576,11 +594,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>59495430148</v>
+          <t>Mariana Ramirez Atehortúa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>59495430148</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -591,11 +611,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flavio</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>60041794183</v>
+          <t>Flavio Moreno</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>60041794183</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -606,11 +628,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>59701500254</v>
+          <t>Carolina Gomez</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>59701500254</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -621,11 +645,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gustavo</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>59785432117</v>
+          <t>Gustavo Bocanegra</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>59785432117</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -636,11 +662,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Julian Esteban</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>59954011144</v>
+          <t>Julian Esteban Hincapie</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>59954011144</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -651,11 +679,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Natalia Maria</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>60292031366</v>
+          <t>Natalia Maria Abdala Gonzalez</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>60292031366</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -666,11 +696,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Erika J</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>60256103180</v>
+          <t>Erika J Álvarez</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>60256103180</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -681,11 +713,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Willyam Leonardo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>59327045746</v>
+          <t>Willyam Leonardo Alcalá Quijano</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>59327045746</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -696,11 +730,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sebastian</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>60120113152</v>
+          <t>Sebastian Serna</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>60120113152</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -711,11 +747,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>60671475634</v>
+          <t>Cecilia Malaver</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>60671475634</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -726,11 +764,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>59792432549</v>
+          <t>Sergio Cadavid</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>59792432549</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -741,11 +781,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yesid</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>60051379811</v>
+          <t>Yesid Lopez</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>60051379811</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -756,11 +798,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>60053477228</v>
+          <t>Carolina Torres</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>60053477228</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -771,11 +815,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>59562397352</v>
+          <t>Carlos Torres</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>59562397352</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -786,11 +832,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yuliana Maria</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>60204869197</v>
+          <t>Yuliana Maria Ayala Lopez</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>60204869197</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -801,11 +849,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yeye</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>59937234601</v>
+          <t>Yeye Naranjo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>59937234601</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -816,11 +866,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jhonatan</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>60036554279</v>
+          <t>Jhonatan Gomez</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>60036554279</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -831,11 +883,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miguel</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>60334270076</v>
+          <t>Miguel Longa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>60334270076</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -846,11 +900,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Johnathan</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>60052551444</v>
+          <t>Johnathan Manco Tobon</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>60052551444</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -861,11 +917,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Luis Miguel</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>59806724174</v>
+          <t>Luis Miguel Bernal</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>59806724174</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -876,11 +934,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>60076455338</v>
+          <t>Carlos Mora</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>60076455338</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -891,11 +951,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mauricio</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>59545538874</v>
+          <t>Mauricio Ramirez</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>59545538874</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -906,11 +968,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>59806320800</v>
+          <t>Oswaldo Maya</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>59806320800</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -921,11 +985,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>60199552919</v>
+          <t>Cesar Morales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>60199552919</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -936,11 +1002,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Valentina</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>59230370955</v>
+          <t>Valentina Restrepo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>59230370955</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -951,11 +1019,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Yuly</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>60676345265</v>
+          <t>Yuly Marcela</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>60676345265</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -966,11 +1036,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gerson Iván</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>60236770726</v>
+          <t>Gerson Iván Duran</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>60236770726</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -981,11 +1053,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wilmar</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>59489816335</v>
+          <t>Wilmar Perez</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>59489816335</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -996,11 +1070,13 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wilver Arley</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>59319398799</v>
+          <t>Wilver Arley Mosquera Vanegas</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>59319398799</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1011,11 +1087,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mauricio</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>60233445305</v>
+          <t>Mauricio Parra</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>60233445305</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1026,11 +1104,13 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Andres</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>59483275180</v>
+          <t>Andres Mejia</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>59483275180</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1041,11 +1121,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Paula Andrea Usuga</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>59235729249</v>
+          <t>Paula Andrea Usuga Espinosa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>59235729249</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1056,11 +1138,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Laura</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>60650851625</v>
+          <t>Laura Mendez</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>60650851625</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1071,11 +1155,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>60076778402</v>
+          <t>Gonzalo Villa Villegas</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>60076778402</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1086,11 +1172,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>60052848720</v>
+          <t>Juan Calle</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>60052848720</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1101,11 +1189,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mauricio</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>60075819854</v>
+          <t>Mauricio Gomez</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>60075819854</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1116,11 +1206,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ingrid</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>60206837554</v>
+          <t>Ingrid Barrera</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>60206837554</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1131,11 +1223,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Luis Alfonso</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>60119199778</v>
+          <t>Luis Alfonso Londoño Castaño</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>60119199778</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1146,11 +1240,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>60204104314</v>
+          <t>Mario Lopez</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>60204104314</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1161,11 +1257,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jaime Rafael Guerrero</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>60049553772</v>
+          <t>Jaime Rafael Guerrero Garcia</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>60049553772</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1176,11 +1274,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>60075823669</v>
+          <t>Juan Zambrano</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>60075823669</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1191,11 +1291,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Catalina</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>59431345024</v>
+          <t>Catalina Rodriguez</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>59431345024</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1206,11 +1308,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jose German</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>60155580236</v>
+          <t>Jose German Cardenas Cruz</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>60155580236</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1221,11 +1325,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alejandro</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>60205750594</v>
+          <t>Alejandro Zapata</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>60205750594</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1236,11 +1342,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>60275067026</v>
+          <t>Juan Montaño Parra</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>60275067026</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1251,11 +1359,13 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alejo</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>60050158487</v>
+          <t>Alejo Arboleda</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>60050158487</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1266,11 +1376,13 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Melani Gisella</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>59155908376</v>
+          <t>Melani Gisella Viveros Morenos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>59155908376</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1281,11 +1393,13 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>60050925469</v>
+          <t>Carolina Lopera Velez</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>60050925469</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1296,11 +1410,13 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Esteban</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>60041918069</v>
+          <t>Esteban Mejia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>60041918069</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1311,11 +1427,13 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luis Alberto</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>60072678250</v>
+          <t>Luis Alberto Herrera</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>60072678250</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1326,11 +1444,13 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gloria</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>60074965037</v>
+          <t>Gloria Cano</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>60074965037</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1341,11 +1461,13 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jesus Gallardo</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>60184866825</v>
+          <t>Jesus Gallardo Mejia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>60184866825</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1356,11 +1478,13 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Julian</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>59649836072</v>
+          <t>Julian Alzate</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>59649836072</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1371,11 +1495,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Arles</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>60295390587</v>
+          <t>Arles Restrepo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>60295390587</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1386,11 +1512,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duvian</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>60075426090</v>
+          <t>Duvian Castano</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>60075426090</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1401,11 +1529,13 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>60152290420</v>
+          <t>John Duque</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>60152290420</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1416,11 +1546,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sebastian Escobar</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>59806664118</v>
+          <t>Sebastian Escobar Freydell</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>59806664118</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1431,11 +1563,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mj-tech</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>60459916544</v>
+          <t>Mj-tech Serna Blandon</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>60459916544</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1446,11 +1580,13 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alberto</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>60164388651</v>
+          <t>Alberto Lasso Arias</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>60164388651</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1461,11 +1597,13 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Saul Antonio</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>60563416109</v>
+          <t>Saul Antonio Chico Torres</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>60563416109</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1476,11 +1614,13 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>60052292458</v>
+          <t>David Gutierrez Rivas</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>60052292458</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1491,11 +1631,13 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Simón Álvarez</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>60222398034</v>
+          <t>Simón Álvarez Villegas</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>60222398034</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1506,11 +1648,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>59332814420</v>
+          <t>Paula Bermudez</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>59332814420</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1521,11 +1665,13 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lina María</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>59375212920</v>
+          <t>Lina María Roldán Botero</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>59375212920</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1536,11 +1682,13 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>60249577827</v>
+          <t>Carolina Jiménez</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>60249577827</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1551,11 +1699,13 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>60110034872</v>
+          <t>Sandra Acosta</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>60110034872</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1566,11 +1716,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Juan David</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>59702228803</v>
+          <t>Juan David Vélez</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>59702228803</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1581,11 +1733,13 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guillermo</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>60241343093</v>
+          <t>Guillermo Escobar Vélez</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>60241343093</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -1596,11 +1750,13 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Paola Andrea</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>59991892125</v>
+          <t>Paola Andrea Patiño</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>59991892125</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -1611,11 +1767,13 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>60128953247</v>
+          <t>Claudia Becerra</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>60128953247</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -1626,11 +1784,13 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edwin G.</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>59478550334</v>
+          <t>Edwin G. Montoya Hoyos</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>59478550334</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -1641,11 +1801,13 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>60165463064</v>
+          <t>Carlos Sánchez</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>60165463064</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -1656,11 +1818,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jorge L</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>59665356600</v>
+          <t>Jorge L Gaviria</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>59665356600</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -1671,11 +1835,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eduar</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>60658507123</v>
+          <t>Eduar Matiz</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>60658507123</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -1686,11 +1852,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Víctor Manuel</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>59483891256</v>
+          <t>Víctor Manuel Cortes Santos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>59483891256</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -1701,11 +1869,13 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>German</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>59472272398</v>
+          <t>German Vargas</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>59472272398</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -1716,11 +1886,13 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Paulina</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>60156958302</v>
+          <t>Paulina Hincapi</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>60156958302</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -1731,11 +1903,13 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Carloa</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>60239413318</v>
+          <t>Carloa Segura</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>60239413318</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -1746,11 +1920,13 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gloria Isabel</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>59576988968</v>
+          <t>Gloria Isabel Daza</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>59576988968</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -1761,11 +1937,13 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Guillermo</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>60330723693</v>
+          <t>Guillermo Patiño</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>60330723693</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -1776,11 +1954,13 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alvaro</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>60315214345</v>
+          <t>Alvaro Moreno</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>60315214345</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -1791,11 +1971,13 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luis German</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>60034343528</v>
+          <t>Luis German Fajardo</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>60034343528</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -1806,11 +1988,13 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Manuela</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>59232842926</v>
+          <t>Manuela Mejia Gomez</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>59232842926</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -1821,11 +2005,13 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Luis Felipe</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>59245417747</v>
+          <t>Luis Felipe Espinal</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>59245417747</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -1836,11 +2022,13 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>60511671945</v>
+          <t>Carolina Vlez</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>60511671945</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -1851,11 +2039,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>60589555261</v>
+          <t>Luis Lovera</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>60589555261</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -1866,11 +2056,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gustavo</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>60074667278</v>
+          <t>Gustavo Orozco</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>60074667278</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -1881,11 +2073,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wilmar</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>60334762297</v>
+          <t>Wilmar Franco</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>60334762297</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -1896,11 +2090,13 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Julian</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>60668203659</v>
+          <t>Julian Ramirez</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>60668203659</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -1911,11 +2107,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fabian Esteban</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>59235204244</v>
+          <t>Fabian Esteban Herrera Herrera</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>59235204244</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -1926,11 +2124,13 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>John Fredy</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>60056034905</v>
+          <t>John Fredy Salazar Arredondo</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>60056034905</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -1941,11 +2141,13 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Andres</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>59686797167</v>
+          <t>Andres Rios</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>59686797167</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -1956,11 +2158,13 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manuela</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>59850832706</v>
+          <t>Manuela Ramirez</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>59850832706</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -1971,11 +2175,13 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Luis Gonzaga</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>60257242204</v>
+          <t>Luis Gonzaga Marin Osorio</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>60257242204</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -1986,11 +2192,13 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Agustín</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>60232212508</v>
+          <t>Agustín Vélez</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>60232212508</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2001,11 +2209,13 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bayron</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>60136677395</v>
+          <t>Bayron Saldarriaga</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>60136677395</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -2016,11 +2226,13 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Catalina</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>59764731700</v>
+          <t>Catalina Gil</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>59764731700</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -2031,11 +2243,13 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tomas</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>60189204010</v>
+          <t>Tomas Rodriguez</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>60189204010</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -2046,11 +2260,13 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Álvaro</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>60259895215</v>
+          <t>Álvaro Gómez Fernández</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>60259895215</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -2061,11 +2277,13 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>60312034370</v>
+          <t>Jordan Alvarez</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>60312034370</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -2076,11 +2294,13 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Juan David</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>59237618024</v>
+          <t>Juan David Quintero</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>59237618024</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -2091,11 +2311,13 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Elver</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>60325277099</v>
+          <t>Elver Martinez</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>60325277099</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -2106,11 +2328,13 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>59474165062</v>
+          <t>Mariana Villa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>59474165062</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -2121,11 +2345,13 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>59490437678</v>
+          <t>Sandra Montoya</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>59490437678</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -2136,11 +2362,13 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Marcial</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>60299440433</v>
+          <t>Marcial Mueses</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>60299440433</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -2151,11 +2379,13 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Luz Mila</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>60077165427</v>
+          <t>Luz Mila Echavarria</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>60077165427</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -2166,11 +2396,13 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Víctor Manuel</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>60180561235</v>
+          <t>Víctor Manuel Turpin Martinez</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>60180561235</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -2181,11 +2413,13 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ana Dely</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>60259969432</v>
+          <t>Ana Dely Espinosa Montoya</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>60259969432</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -2196,11 +2430,13 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>José Fernando</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>60643427445</v>
+          <t>José Fernando Tobías</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>60643427445</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -2211,11 +2447,13 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Adriana</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>60299977061</v>
+          <t>Adriana Botia</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>60299977061</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -2226,11 +2464,13 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>60540220463</v>
+          <t>Daniel Quiintero</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>60540220463</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -2241,11 +2481,13 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hernando</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>60314609228</v>
+          <t>Hernando Mejia Restrepo</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>60314609228</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -2256,11 +2498,13 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Juliana</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>60591741331</v>
+          <t>Juliana Gutierrez Giraldo</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>60591741331</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -2271,11 +2515,13 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mariano</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>60292651541</v>
+          <t>Mariano Hernández Camargo</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>60292651541</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -2286,11 +2532,13 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ismael</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>60050827943</v>
+          <t>Ismael Restrepo Correa</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>60050827943</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -2301,11 +2549,13 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Carlos Manuel</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>60202537050</v>
+          <t>Carlos Manuel Uribe</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>60202537050</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -2316,11 +2566,13 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jose Alejandro</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>60041219106</v>
+          <t>Jose Alejandro Zuluaga Salazar</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>60041219106</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -2331,11 +2583,13 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Victor Eduardo</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>59318655264</v>
+          <t>Victor Eduardo Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>59318655264</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -2346,11 +2600,13 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Hector Andres</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>59853181218</v>
+          <t>Hector Andres Pelaez</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>59853181218</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -2361,11 +2617,13 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Alejo</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>60305729324</v>
+          <t>Alejo Pérez</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>60305729324</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -2376,11 +2634,13 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Walter</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>59437802061</v>
+          <t>Walter Gómez</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>59437802061</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -2391,11 +2651,13 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Maria Paula</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>60054003021</v>
+          <t>Maria Paula Rincón Castaño</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>60054003021</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -2406,11 +2668,13 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Maria V</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>60600958094</v>
+          <t>Maria V Campo</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>60600958094</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -2421,11 +2685,13 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Carlos Andrés Palacios Agudelo</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>60105955844</v>
+          <t>Carlos Andrés Palacios Agudelo Palacio Agudelo</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>60105955844</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -2436,11 +2702,13 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>59328663993</v>
+          <t>Angela Gómez Buitrago</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>59328663993</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -2451,11 +2719,13 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>60651427155</v>
+          <t>Paula Agámez Marchena</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>60651427155</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -2466,11 +2736,13 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Margarita</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>60334578761</v>
+          <t>Margarita Castro</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>60334578761</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -2481,11 +2753,13 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Katherinne</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>59462319189</v>
+          <t>Katherinne Gallego</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>59462319189</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -2496,11 +2770,13 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Julio Cesar</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>60560808319</v>
+          <t>Julio Cesar Gutierrez Fonseca</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>60560808319</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -2511,11 +2787,13 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Manuel José</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>60666927909</v>
+          <t>Manuel José Urueta</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>60666927909</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -2526,11 +2804,13 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Natalia</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>60314887335</v>
+          <t>Natalia Grajales Rua</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>60314887335</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -2541,11 +2821,13 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>60058002465</v>
+          <t>Daniel Hernandez</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>60058002465</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -2556,11 +2838,13 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ana</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>60239620749</v>
+          <t>Ana Cecilia Restrepo Alvarez</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>60239620749</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -2571,11 +2855,13 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Jaime</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>59686268807</v>
+          <t>Jaime Rodriguez Zamora</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>59686268807</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -2586,11 +2872,13 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Franco Andres</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>59575644023</v>
+          <t>Franco Andres Pantoja Santacruz</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>59575644023</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -2601,11 +2889,13 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>59389873247</v>
+          <t>Luis Trujillo</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>59389873247</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -2616,11 +2906,13 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Luzedi</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>60237826981</v>
+          <t>Luzedi Garciagarcia</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>60237826981</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -2631,11 +2923,13 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Juan Felipe</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>59548967568</v>
+          <t>Juan Felipe Velez Alvarez</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>59548967568</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -2646,11 +2940,13 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Filadelfo</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>60540227445</v>
+          <t>Filadelfo Loboa Caicedo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>60540227445</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -2661,11 +2957,13 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Juan Pablo</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>60709179932</v>
+          <t>Juan Pablo Gómez Escorcia</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>60709179932</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -2676,11 +2974,13 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>60239143534</v>
+          <t>Carlos V</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>60239143534</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -2691,11 +2991,13 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cerli Mildrey</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>60254710620</v>
+          <t>Cerli Mildrey Hoyos Gomez</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>60254710620</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -2706,11 +3008,13 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ivon</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>59386982665</v>
+          <t>Ivon Gonzalez</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>59386982665</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -2721,11 +3025,13 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>María</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>60073985286</v>
+          <t>María Rendon</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>60073985286</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -2736,11 +3042,13 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>59124234093</v>
+          <t>Carlos Mario Pérez</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>59124234093</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -2751,11 +3059,13 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Federico</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>59463287737</v>
+          <t>Federico Suescún Bedoya</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>59463287737</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -2766,11 +3076,13 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Juan David</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>60077530900</v>
+          <t>Juan David Cardeño Rengifo</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>60077530900</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -2781,11 +3093,13 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Antonio José</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>59702666893</v>
+          <t>Antonio José Contreras</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>59702666893</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -2796,11 +3110,13 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mauricio</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>60349215770</v>
+          <t>Mauricio Bohorquez Orozco</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>60349215770</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -2811,11 +3127,13 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Javier Mauricio</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>60051703362</v>
+          <t>Javier Mauricio Hernández Castro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>60051703362</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -2826,11 +3144,13 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>60269121883</v>
+          <t>Sandra Bolívar</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>60269121883</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -2841,11 +3161,13 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>59806677899</v>
+          <t>Juan D. Arboleda</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>59806677899</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -2856,11 +3178,13 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Andrés</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>59805321906</v>
+          <t>Andrés Zuluaga</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>59805321906</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -2871,11 +3195,13 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jorge Armando</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>59530935216</v>
+          <t>Jorge Armando Gallego Diaz</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>59530935216</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -2886,11 +3212,13 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>John Jairo</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>60176873850</v>
+          <t>John Jairo Uribe</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>60176873850</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -2901,11 +3229,13 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Gloria</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>60141710372</v>
+          <t>Gloria Henao</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>60141710372</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -2916,11 +3246,13 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Luis Vasquez Hipnoterapeuta Y Coach En</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>59666417047</v>
+          <t>Luis Vasquez Hipnoterapeuta Y Coach En Pnl</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>59666417047</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -2931,11 +3263,13 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tomás Moncada</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>59419990935</v>
+          <t>Tomás Moncada Mesa</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>59419990935</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -2946,11 +3280,13 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Laura</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>60533453708</v>
+          <t>Laura Martinez Agudelo</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>60533453708</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -2961,11 +3297,13 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Juliana</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>59467409049</v>
+          <t>Juliana Serna</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>59467409049</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -2976,11 +3314,13 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raymond</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>60561781626</v>
+          <t>Raymond Rubin</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>60561781626</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -2991,11 +3331,13 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Elias</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>60271874078</v>
+          <t>Elias Uriana</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>60271874078</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -3006,11 +3348,13 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>59131347460</v>
+          <t>Daniel Torres</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>59131347460</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -3021,11 +3365,13 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Javier</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>60200643725</v>
+          <t>Javier Pareja</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>60200643725</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -3036,11 +3382,13 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Johanna</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>60052530800</v>
+          <t>Johanna Molina</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>60052530800</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -3051,11 +3399,13 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Diego</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>60237899961</v>
+          <t>Diego Hoyos</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>60237899961</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -3066,11 +3416,13 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Emilia</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>59498831757</v>
+          <t>Emilia Rodriguez</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>59498831757</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -3081,11 +3433,13 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Alejandra</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>59806409362</v>
+          <t>Alejandra Escobar</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>59806409362</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -3096,11 +3450,13 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jonathan Andres</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>59497202815</v>
+          <t>Jonathan Andres Rua Penagos</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>59497202815</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -3111,11 +3467,13 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Luz</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>60593145921</v>
+          <t>Luz Almanza</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>60593145921</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -3126,11 +3484,13 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>60174763058</v>
+          <t>Jesús Velasquez Giraldo</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>60174763058</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -3141,11 +3501,13 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jorge René</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>60052791562</v>
+          <t>Jorge René Estupiñán Guzmán</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>60052791562</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -3156,11 +3518,13 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Elena Beatriz</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>60689664914</v>
+          <t>Elena Beatriz De La Hoz Osorio</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>60689664914</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -3171,11 +3535,13 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Adriana</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>59941198142</v>
+          <t>Adriana Pineda Arango</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>59941198142</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -3186,11 +3552,13 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Alejandro</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>59445649017</v>
+          <t>Alejandro Hinestrosa</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>59445649017</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -3201,11 +3569,13 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>60238763899</v>
+          <t>Angela Santa</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>60238763899</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -3216,11 +3586,13 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fabio</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>60689392984</v>
+          <t>Fabio Ruiz Galeano</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>60689392984</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -3231,11 +3603,13 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Felipe</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>60217997934</v>
+          <t>Felipe Delgado Restrepo</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>60217997934</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -3246,11 +3620,13 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Guillermo</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>59806329102</v>
+          <t>Guillermo Rodriguez</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>59806329102</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -3261,11 +3637,13 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Gladimir</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>60334572168</v>
+          <t>Gladimir Zanoja</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>60334572168</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -3276,11 +3654,13 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jose Jaime</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>60050949464</v>
+          <t>Jose Jaime Cifuentes Gonzalez</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>60050949464</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -3291,11 +3671,13 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Andy</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>60074269823</v>
+          <t>Andy Lozano</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>60074269823</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -3306,11 +3688,13 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Luis Alejandro</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>59031904880</v>
+          <t>Luis Alejandro Guzmán Gomez</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>59031904880</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -3321,11 +3705,13 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Delio</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>60387906896</v>
+          <t>Delio Salgdo</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>60387906896</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -3336,11 +3722,13 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Natalia</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>60165683361</v>
+          <t>Natalia Mesa Martínez</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>60165683361</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -3351,11 +3739,13 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>59470911295</v>
+          <t>David Rodríguez</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>59470911295</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -3366,11 +3756,13 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Juan Angel</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>59459402851</v>
+          <t>Juan Angel Soto Aristizabal</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>59459402851</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -3381,11 +3773,13 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Luz</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>60613369720</v>
+          <t>Luz Velasquez</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>60613369720</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -3396,11 +3790,13 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ana Beatriz</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>60164641447</v>
+          <t>Ana Beatriz Agudelo Vélez</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>60164641447</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -3411,11 +3807,13 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sandra Patricia</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>60155714737</v>
+          <t>Sandra Patricia León Cruz</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>60155714737</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -3426,11 +3824,13 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Beatriz Helena</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>59697038946</v>
+          <t>Beatriz Helena Patiño Avendaño</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>59697038946</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -3441,11 +3841,13 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Leon Augusto</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>59331274014</v>
+          <t>Leon Augusto Martínez Giraldo</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>59331274014</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -3456,11 +3858,13 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Carlos Alberto</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>60270592295</v>
+          <t>Carlos Alberto Calle Echavarria</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>60270592295</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -3471,11 +3875,13 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Marta Cecilia</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>60260012890</v>
+          <t>Marta Cecilia Rivas Durango</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>60260012890</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -3486,11 +3892,13 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Edgar</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>59574513284</v>
+          <t>Edgar Cabrera</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>59574513284</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -3501,11 +3909,13 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Eddie</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>59523350934</v>
+          <t>Eddie Parada</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>59523350934</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -3516,11 +3926,13 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Johanna Marcela</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>60445218411</v>
+          <t>Johanna Marcela Fernández Echeverri</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>60445218411</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -3531,11 +3943,13 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>José Nelson</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>60327641876</v>
+          <t>José Nelson Cicery</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>60327641876</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -3546,11 +3960,13 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jorge Eduardo</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>60196455786</v>
+          <t>Jorge Eduardo Jimenez Castañeda</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>60196455786</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -3561,11 +3977,13 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Iván Darío</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>59695115423</v>
+          <t>Iván Darío Salamanca Castro</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>59695115423</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -3576,11 +3994,13 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Adriana Patricia</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>60204414255</v>
+          <t>Adriana Patricia Sanchez Alvarez</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>60204414255</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -3591,11 +4011,13 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Catalina</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>59681481620</v>
+          <t>Catalina Delgado</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>59681481620</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -3606,11 +4028,13 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cesar Fernando</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>60050448171</v>
+          <t>Cesar Fernando Rojas Guevara</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>60050448171</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -3621,11 +4045,13 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>59757415683</v>
+          <t>Claudia Martinez</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>59757415683</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -3636,11 +4062,13 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vanessa</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>60673776423</v>
+          <t>Vanessa Jiménez</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>60673776423</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -3651,11 +4079,13 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Aima Valentina</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>60604378181</v>
+          <t>Aima Valentina Arias Perez</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>60604378181</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -3666,11 +4096,13 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>60466678062</v>
+          <t>Christian Salinas</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>60466678062</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -3681,11 +4113,13 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Dr. Oscar</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
-        <v>60218918163</v>
+          <t>Dr. Oscar Aristizabal</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>60218918163</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -3696,11 +4130,13 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>60530577336</v>
+          <t>Sandra Serna</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>60530577336</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -3711,11 +4147,13 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>60173093739</v>
+          <t>Sergio Andres Cardona</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>60173093739</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -3726,11 +4164,13 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Fabian Andres</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>59838408290</v>
+          <t>Fabian Andres Callejas Varela</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>59838408290</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -3741,11 +4181,13 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jenny</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
-        <v>60167225418</v>
+          <t>Jenny Miranda</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>60167225418</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -3756,11 +4198,13 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>60665693786</v>
+          <t>Mariana Florez Urrego</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>60665693786</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -3771,11 +4215,13 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>59312686736</v>
+          <t>David Cañón</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>59312686736</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -3786,11 +4232,13 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Angélica</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>60201387573</v>
+          <t>Angélica Osorio Tamayo</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>60201387573</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -3801,11 +4249,13 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
-        <v>60531476845</v>
+          <t>Sergio Lopez</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>60531476845</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -3816,11 +4266,13 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="C227" t="n">
-        <v>60713209695</v>
+          <t>Fernando Ceballos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>60713209695</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -3831,11 +4283,13 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Felipe Garzón</t>
-        </is>
-      </c>
-      <c r="C228" t="n">
-        <v>60014165825</v>
+          <t>Felipe Garzón Cristancho</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>60014165825</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -3846,11 +4300,13 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="C229" t="n">
-        <v>59479630689</v>
+          <t>Luis Arias</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>59479630689</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -3861,11 +4317,13 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Eduardo Arias Cadavid</t>
-        </is>
-      </c>
-      <c r="C230" t="n">
-        <v>59216705843</v>
+          <t>Eduardo Arias Cadavid Arias Cadavid</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>59216705843</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -3876,11 +4334,13 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
-        <v>60334006187</v>
+          <t>Juan Zuñiga</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>60334006187</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -3891,11 +4351,13 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Karina</t>
-        </is>
-      </c>
-      <c r="C232" t="n">
-        <v>59806484576</v>
+          <t>Karina Cardona</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>59806484576</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -3906,11 +4368,13 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Esteban Bautista</t>
-        </is>
-      </c>
-      <c r="C233" t="n">
-        <v>59679101225</v>
+          <t>Esteban Bautista Clavijo</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>59679101225</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -3921,11 +4385,13 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Johanna</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>60051421298</v>
+          <t>Johanna Torres</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>60051421298</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -3936,11 +4402,13 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
-        <v>60146426227</v>
+          <t>Juan Bohórquez</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>60146426227</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -3951,11 +4419,13 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cristian Camilo</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>59538457660</v>
+          <t>Cristian Camilo Sierra</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>59538457660</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -3966,11 +4436,13 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>60420884514</v>
+          <t>Daniel Restrepo</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>60420884514</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -3981,11 +4453,13 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>59841187908</v>
+          <t>Juan Salas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>59841187908</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -3996,11 +4470,13 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dra. Viviana Cortes</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>60315621674</v>
+          <t>Dra. Viviana Cortes Franco</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>60315621674</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -4011,11 +4487,13 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Alejandra Marcela</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>60074512813</v>
+          <t>Alejandra Marcela Garcia Rios</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>60074512813</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -4026,11 +4504,13 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dora</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>60077025360</v>
+          <t>Dora Cecilia Perez Pulgarin</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>60077025360</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -4041,11 +4521,13 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Angel</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
-        <v>59122588777</v>
+          <t>Angel Fabricio Concejal</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>59122588777</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -4056,11 +4538,13 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Fundacion</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
-        <v>60238908573</v>
+          <t>Fundacion Humana</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>60238908573</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -4071,11 +4555,13 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Yazmin</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>60696265378</v>
+          <t>Yazmin Sucerquia</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>60696265378</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -4086,11 +4572,13 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Liliana</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>60055063924</v>
+          <t>Liliana Cabrales</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>60055063924</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -4101,11 +4589,13 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Enith Teresa</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>60656933724</v>
+          <t>Enith Teresa Pasos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>60656933724</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -4116,11 +4606,13 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Amparo</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>59806415887</v>
+          <t>Amparo González</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>59806415887</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -4131,11 +4623,13 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Giovanni</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>60073946917</v>
+          <t>Giovanni Salas Araque</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>60073946917</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -4146,11 +4640,13 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Mara Camila</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>59769959290</v>
+          <t>Mara Camila Chaparro</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>59769959290</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -4161,11 +4657,13 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Blanca</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>60074181485</v>
+          <t>Blanca Zapata</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>60074181485</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -4176,11 +4674,13 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Juliana</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>60631112118</v>
+          <t>Juliana Morales Cañón</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>60631112118</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -4191,11 +4691,13 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Gerardo</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
-        <v>59481178461</v>
+          <t>Gerardo Plazas Sanchez</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>59481178461</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -4206,11 +4708,13 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>59793467486</v>
+          <t>David Agudelo</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>59793467486</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -4221,11 +4725,13 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Gustavo</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>59559782984</v>
+          <t>Gustavo Adolfo Santa</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>59559782984</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -4236,11 +4742,13 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Ruben</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>59759610218</v>
+          <t>Ruben Medina</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>59759610218</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -4251,11 +4759,13 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Shirley</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>60075342520</v>
+          <t>Shirley Puello</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>60075342520</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -4266,11 +4776,13 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Pili</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
-        <v>59700476680</v>
+          <t>Pili Gutiérrez</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>59700476680</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -4281,11 +4793,13 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Francisco</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>60403359092</v>
+          <t>Francisco Castillo</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>60403359092</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -4296,11 +4810,13 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Eliana</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>59552681479</v>
+          <t>Eliana Bedoya</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>59552681479</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -4311,11 +4827,13 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Juan Carlos</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
-        <v>59806694766</v>
+          <t>Juan Carlos Escobar</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>59806694766</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -4326,11 +4844,13 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Daniel Jose</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
-        <v>60401334136</v>
+          <t>Daniel Jose Rudas</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>60401334136</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -4341,11 +4861,13 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Yamile Chica</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
-        <v>59659046186</v>
+          <t>Yamile Chica Rodriguez</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>59659046186</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -4356,11 +4878,13 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Natalia Gallego</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>59806642054</v>
+          <t>Natalia Gallego Vallejo</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>59806642054</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -4371,11 +4895,13 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Maria Paulina</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>60219150914</v>
+          <t>Maria Paulina Perez Sierra</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>60219150914</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -4386,11 +4912,13 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>María Elena</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>60164942406</v>
+          <t>María Elena Yepes</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>60164942406</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -4401,11 +4929,13 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Lina Maria</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>60240124555</v>
+          <t>Lina Maria Pérez Uribe</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>60240124555</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -4416,11 +4946,13 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Katherine Trespalacios</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>59752419965</v>
+          <t>Katherine Trespalacios Madrid</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>59752419965</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -4431,11 +4963,13 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Jacobo</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>60239726961</v>
+          <t>Jacobo Maya G</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>60239726961</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -4446,11 +4980,13 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Joaquin</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>60466901112</v>
+          <t>Joaquin Rivera Caro</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>60466901112</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -4461,11 +4997,13 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Javier</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
-        <v>59337280940</v>
+          <t>Javier Zapata</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>59337280940</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -4476,11 +5014,13 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>60074206348</v>
+          <t>Marta Rios</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>60074206348</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -4491,11 +5031,13 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nury Johana</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>57979973155</v>
+          <t>Nury Johana Sandoval</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>57979973155</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -4506,11 +5048,13 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>59272935535</v>
+          <t>Carlos Rodriguez</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>59272935535</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -4521,11 +5065,13 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Alexandra Grisales Vahos</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>60253550420</v>
+          <t>Alexandra Grisales Vahos Alexandra Grisales Vahos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>60253550420</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -4536,11 +5082,13 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Remberto Luis</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>60063314025</v>
+          <t>Remberto Luis Rhenals Garrido</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>60063314025</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -4551,11 +5099,13 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>59476487582</v>
+          <t>Jose Gaviria</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>59476487582</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -4566,11 +5116,13 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Jorge</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>60294354789</v>
+          <t>Jorge Ángel</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>60294354789</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -4581,11 +5133,13 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Maria Alexandra</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>60180122112</v>
+          <t>Maria Alexandra Ayala Lopez</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>60180122112</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -4596,11 +5150,13 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>59806536881</v>
+          <t>Juan Arango</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>59806536881</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -4611,11 +5167,13 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>60143326059</v>
+          <t>Sandra Campos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>60143326059</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -4626,11 +5184,13 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sergio Andrés</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>60050675467</v>
+          <t>Sergio Andrés Vásquez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>60050675467</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -4641,11 +5201,13 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sebastian</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>60187947172</v>
+          <t>Sebastian Quintero Duque</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>60187947172</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -4656,11 +5218,13 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Juanes</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>60532011823</v>
+          <t>Juanes Restrepo</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>60532011823</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -4671,11 +5235,13 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>60153435969</v>
+          <t>David Ramirez</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>60153435969</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -4686,11 +5252,13 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Natalia Andrea</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>59728016457</v>
+          <t>Natalia Andrea Muñoz Valero</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>59728016457</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -4701,11 +5269,13 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>David Llano</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>59432784725</v>
+          <t>David Llano Cortes</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>59432784725</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -4716,11 +5286,13 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Natalia</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>60023008891</v>
+          <t>Natalia Machado Román</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>60023008891</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -4731,11 +5303,13 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Daniela</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>59806677898</v>
+          <t>Daniela Flórez</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>59806677898</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -4746,11 +5320,13 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Andres Felipe</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>60041216799</v>
+          <t>Andres Felipe Palacio Montoya</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>60041216799</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -4761,11 +5337,13 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Jesus David</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>60056360788</v>
+          <t>Jesus David Ramirez Sanchez</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>60056360788</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -4776,11 +5354,13 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>José</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>60239414273</v>
+          <t>José Hernandez</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>60239414273</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -4791,11 +5371,13 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>60115300789</v>
+          <t>Santiago Castano</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>60115300789</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -4806,11 +5388,13 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>60139953301</v>
+          <t>Santiago Suarez Triana</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>60139953301</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -4821,11 +5405,13 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>59805097528</v>
+          <t>Andrea Ocampo</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>59805097528</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -4836,11 +5422,13 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Yaky</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>60607024481</v>
+          <t>Yaky Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>60607024481</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -4851,11 +5439,13 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Isaias</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>60219075355</v>
+          <t>Isaias Barrios</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>60219075355</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -4866,11 +5456,13 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Laura Giraldo</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>59267526955</v>
+          <t>Laura Giraldo Sarasa</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>59267526955</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -4881,11 +5473,13 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Ricardo</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>60074626698</v>
+          <t>Ricardo Meneses</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>60074626698</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -4896,11 +5490,13 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Angie Tatiana</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>60097461867</v>
+          <t>Angie Tatiana Escobar Franco</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>60097461867</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -4911,11 +5507,13 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Gabriel</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>60160456212</v>
+          <t>Gabriel Naranjo Pizano</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>60160456212</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -4926,11 +5524,13 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Julian</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>59421061539</v>
+          <t>Julian Arboleda</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>59421061539</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -4941,11 +5541,13 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>59720649354</v>
+          <t>Daniel Flórez</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>59720649354</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -4956,11 +5558,13 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lina</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>60106875224</v>
+          <t>Lina Barrera</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>60106875224</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -4971,11 +5575,13 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ricardo</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>60076679786</v>
+          <t>Ricardo Alba</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>60076679786</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -4986,11 +5592,13 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Luis Orlando</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>60077085452</v>
+          <t>Luis Orlando Yepes Tabares</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>60077085452</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -5001,11 +5609,13 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Ana Maria</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>60551017732</v>
+          <t>Ana Maria Álvarez Restrepo</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>60551017732</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -5016,11 +5626,13 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>60013864628</v>
+          <t>Katherine Payares</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>60013864628</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -5031,11 +5643,13 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Jorge</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>60304489739</v>
+          <t>Jorge Jaramillo</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>60304489739</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -5046,11 +5660,13 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Shirley Johana</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>59548508849</v>
+          <t>Shirley Johana Munera Rua</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>59548508849</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -5061,11 +5677,13 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ana Maria</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>60379234216</v>
+          <t>Ana Maria Alvarez Fernandez</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>60379234216</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -5076,11 +5694,13 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Camila</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>60632046370</v>
+          <t>Camila Bedoya</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>60632046370</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -5091,11 +5711,13 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>60079679059</v>
+          <t>Alex Florez Garcia</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>60079679059</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -5106,11 +5728,13 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Enzo</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>60453620547</v>
+          <t>Enzo Marchese</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>60453620547</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -5121,11 +5745,13 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Laura Mercadeo</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>60059102390</v>
+          <t>Laura Mercadeo Prueba Aguilar</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>60059102390</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -5136,11 +5762,13 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Rick</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>59570932624</v>
+          <t>Rick Pabon</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>59570932624</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -5151,11 +5779,13 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Laura</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>60539594514</v>
+          <t>Laura Martinez</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>60539594514</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -5166,11 +5796,13 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>59570787255</v>
+          <t>Juan Or.mm</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>59570787255</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -5181,11 +5813,13 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>60074896916</v>
+          <t>Monica De La Hoz</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>60074896916</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -5196,11 +5830,13 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cielo</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>60676243800</v>
+          <t>Cielo Rios</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>60676243800</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -5211,11 +5847,13 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Álvaro Fernando</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>60139210154</v>
+          <t>Álvaro Fernando Portilla Araujo</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>60139210154</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -5226,11 +5864,13 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>59332807266</v>
+          <t>Daniel Arango</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>59332807266</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -5241,11 +5881,13 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Juanjose Galvis</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>59247487496</v>
+          <t>Juanjose Galvis González</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>59247487496</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/campaign_Vive_Living.xlsx
+++ b/output/campaign_Vive_Living.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5774,117 +5774,100 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>573043460864</t>
+          <t>573124457430</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Laura Martinez</t>
+          <t>Juan Or.mm</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>60539594514</t>
+          <t>59570787255</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>573124457430</t>
+          <t>573127938080</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Juan Or.mm</t>
+          <t>Monica De La Hoz</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>59570787255</t>
+          <t>60074896916</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>573127938080</t>
+          <t>573187620912</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Monica De La Hoz</t>
+          <t>Cielo Rios</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>60074896916</t>
+          <t>60676243800</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>573187620912</t>
+          <t>573205309193</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cielo Rios</t>
+          <t>Álvaro Fernando Portilla Araujo</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>60676243800</t>
+          <t>60139210154</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>573205309193</t>
+          <t>573006545177</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Álvaro Fernando Portilla Araujo</t>
+          <t>Daniel Arango</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>60139210154</t>
+          <t>59332807266</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>573006545177</t>
+          <t>573116204753</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Daniel Arango</t>
+          <t>Juanjose Galvis González</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
-        <is>
-          <t>59332807266</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>573116204753</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Juanjose Galvis González</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
         <is>
           <t>59247487496</t>
         </is>
